--- a/start-iids/data/reference/RP7.3_D020_partial_year_data_collection.xlsx
+++ b/start-iids/data/reference/RP7.3_D020_partial_year_data_collection.xlsx
@@ -7,10 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Istruzioni" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Metadati_periodo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="D020_2025_periodo" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="D020_2022_omologo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="00_Contesto" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="01_Istruzioni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="02_Metadati_periodo" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03_D020_2025_periodo" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="04_D020_2022_omologo" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="05_Mappatura_modello" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="06_Validazione" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -30,13 +33,12 @@
     </font>
     <font>
       <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color rgb="000B5A3C"/>
+      <sz val="14"/>
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000B5A3C"/>
       <sz val="11"/>
     </font>
     <font>
@@ -45,6 +47,7 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="000B5A3C"/>
       <sz val="12"/>
     </font>
   </fonts>
@@ -97,17 +100,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -474,153 +482,171 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:A26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="112" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RP7.3 — Raccolta dati D020 (anno parziale 2025) — riconciliazione opzione A</t>
+          <t>Progetto START — RP7.3 · Scheda di raccolta dati reali: D020 (anno parziale 2025)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Motivo: D020 (Viano) ha cessato le attività a luglio 2025 (riconversione a polo logistico).</t>
+          <t>1) Contesto di progetto</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Il 2025 di D020 è quindi un periodo PARZIALE (gennaio → data di cessazione), non un anno pieno.</t>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>START (MIMIT, DM 31/12/2021) guida la transizione dell'industria ceramica da Industria 4.0 a Intelligent Industry</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>in chiave di sostenibilità. L'OR7 valida in ambiente operativo gli strumenti; la RP7.3 (Assessment termodinamico</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Metodo adottato (opzione A — riferimento omologo): per D020 2025 il riferimento di ciascun modulo</t>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>della fabbrica) applica il modello EEA+ per calcolare l'Indice Termodinamico di Sostenibilità (TSI) di D020, D060, D240.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>è il 2022 sullo STESSO periodo (gennaio → data di cessazione), non il 2022 annuale.</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Questo rende TSI_abs, Φ e Ψ confrontabili (sono rapporti) ed evita che la minore durata</t>
+          <t>2) Il fatto da recepire</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>dell'esercizio appaia come un miglioramento.</t>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>L'unità D020 (Viano) ha prodotto solo per una parte del 2025 e ha CESSATO le attività a LUGLIO 2025 (riconversione</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>a polo logistico), come da RP7.5 §1.2 e collaudo RP7.8. Dal 2026 il perimetro è D060 + D240. Il 2025 di D020 è</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Cosa serve: compilare la colonna 'VALORE REALE' per DUE periodi omologhi:</t>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>quindi un PERIODO PARZIALE (gennaio → data di cessazione), non un anno pieno.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • D020 2025: gennaio → data esatta di cessazione;</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • D020 2022: gennaio → stessa data di cessazione (stesso numero di mesi/giorni).</t>
+          <t>3) Metodo adottato — opzione A (riferimento omologo) — ADR-015</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Per D020 2025 il riferimento di ciascun modulo è il 2022 sullo STESSO periodo (gennaio → data di cessazione), non</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Regole:</t>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>il 2022 annuale. Così TSI_abs, Φ e Ψ (rapporti) restano confrontabili e la minore durata NON appare come miglioramento.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Dati MISURATI, non stimati. NON ricavare i valori dall'anno pieno per quota di mesi.</t>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Le grandezze estensive (f_i, SA, Ex_ref, produzione) del periodo NON sono confrontabili con gli anni pieni.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Se un dato non è disponibile, lasciarlo vuoto e annotarlo (non inventarlo).</t>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>La guardia 'TEMPORAL_MISMATCH' blocca il confronto fra finestre di durata diversa.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  • Unità: energia elettrica in kWh (inclusa autoproduzione da cogeneratore); gas in Nm³;</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">    termini dei moduli in MJ; produzione in m²; Ψ adimensionale.</t>
+          <t>4) Scopo di questa scheda</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Raccogliere i DATI REALI MISURATI dei DUE periodi omologhi (D020 2025 gen→cessazione e D020 2022 stesso intervallo)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>La colonna 'valore provvisorio (in uso)' mostra i valori ORA usati per collaudare il modello</t>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>con cui sostituire i valori PROVVISORI oggi usati solo per collaudare il modello. Alla consegna si rigenera il log</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>(scalatura del profilo mensile): vanno SOSTITUITI con i valori reali, non riusati.</t>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>beta-1.2 e si aggiorna la RP7.3 a RV.2; a valle vanno rigenerate RP7.8 e (se pertinente) RP8.6.</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
+      <c r="A23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Riferimenti: Manuali operativi moduli TEI-J/EFA-J/EcoFA-J/SFA-J; ADR-015; istruzioni RP7.3.</t>
+          <t>5) Agganci documentali</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Piano di Sviluppo START (OR7, Attività 7.3) · RP7.3 · RP7.5 §1.2 · RP7.8 · RP6.1/6.2/6.3/6.4/6.5 · Manuali TEI-J/</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EFA-J/EcoFA-J/SFA-J · ADR-012, ADR-013, ADR-015.</t>
         </is>
       </c>
     </row>
@@ -635,121 +661,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="118" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>campo</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>descrizione</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>VALORE REALE (da compilare)</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Istruzioni di compilazione</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>data_cessazione_D020</t>
-        </is>
-      </c>
-      <c r="B2" s="5" t="inlineStr">
-        <is>
-          <t>Giorno esatto di cessazione attività D020 (AAAA-MM-GG)</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr"/>
+      <c r="A2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>periodo_2025_inizio</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>Inizio periodo 2025 (tipic. 2025-01-01)</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Compilare i fogli '03_D020_2025_periodo' e '04_D020_2022_omologo' (colonna gialla 'VALORE REALE').</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>periodo_2025_fine</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>Fine periodo 2025 = data di cessazione</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Prima compilare '02_Metadati_periodo' (data esatta di cessazione e finestre temporali).</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>periodo_2022_inizio</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Inizio periodo omologo 2022 (2022-01-01)</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr"/>
+      <c r="A5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>periodo_2022_fine</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Fine periodo omologo 2022 (stesso giorno/mese della cessazione)</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr"/>
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Regole tassative:</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>mesi_attivi</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>N° mesi attivi nel periodo (es. 7)</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>• Dati MISURATI dai sistemi aziendali (ERP/MES/HSE), NON stimati.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>fonte_dati</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Sistema/fonte dei dati (ERP/MES, modulo, estrazione)</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>• NON ricavare i valori dall'anno pieno per quota di mesi (riproporzionamento VIETATO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>• I DUE periodi devono avere la STESSA finestra (stesso giorno/mese di inizio e fine).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>• Dato non disponibile → lasciare VUOTO e annotarlo (non inventare).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Unità di misura:</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>• produzione = m² · gas = Nm³ · elettricità = kWh (incl. autoproduzione) · termini moduli = MJ · Ψ = adim.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>• Convenzione del modello: calcolo interno in MJ, output in GJ (÷1.000). Exergia gas = exergia CHIMICA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>La colonna grigia 'valore provvisorio (in uso)' è solo ordine di grandezza e VA SOSTITUITA con i valori reali.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Consegna: restituire il file compilato; verrà caricato in data/reference e rieseguito 'python3 -m src.run_all'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Vedere '05_Mappatura_modello' (dove finisce ogni valore) e '06_Validazione' (controlli e criteri di chiusura).</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -762,606 +788,150 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>D020 — periodo gennaio→cessazione 2025 (da compilare)</t>
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>descrizione</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>VALORE REALE (da compilare)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>note</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>campo</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>modulo</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>descrizione</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>unità</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>VALORE REALE (da compilare)</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>valore provvisorio (in uso, da sostituire)</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>data_cessazione_D020</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Giorno esatto di cessazione attività D020 (AAAA-MM-GG)</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr"/>
+      <c r="D2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>produzione_m2</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
-        <is>
-          <t>produzione</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>Produzione del periodo</t>
-        </is>
-      </c>
-      <c r="D3" s="5" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="8" t="n">
-        <v>2382600</v>
-      </c>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>periodo_2025_inizio</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>Inizio periodo 2025 (tipic. 2025-01-01)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>V_gas_Nm3</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Gas naturale consumato nel periodo</t>
-        </is>
-      </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t>Nm³</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="8" t="n">
-        <v>2201068</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>periodo_2025_fine</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Fine periodo 2025 = data di cessazione</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
+      <c r="D4" s="6" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>E_el_kWh</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Energia elettrica (inclusa autoproduzione)</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
-        <is>
-          <t>kWh</t>
-        </is>
-      </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="8" t="n">
-        <v>6419783</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>periodo_2022_inizio</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>Inizio periodo omologo 2022 (2022-01-01)</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+      <c r="D5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>loss_MTS_MJ</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>TEI-J</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>TEI — perdita exergetica stadio MTS (spray-dryer)</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="8" t="n">
-        <v>31064339</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
+          <t>periodo_2022_fine</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Fine periodo omologo 2022 (stesso giorno/mese della cessazione)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+      <c r="D6" s="6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>loss_MTO_MJ</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>TEI-J</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>TEI — perdita exergetica stadio MTO (forming/kiln/finishing)</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="8" t="n">
-        <v>26922427</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
+          <t>mesi_attivi</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>N° mesi attivi nel periodo (es. 7)</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+      <c r="D7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>inv_MJ</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>TEI-J</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità exergetica invenduto</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>3174624</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>giorni_attivi</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>N° giorni attivi (per il controllo di durata ≤2 gg)</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+      <c r="D8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>qual_MTS_MJ</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>TEI-J</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità qualità corpo (MTS)</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="8" t="n">
-        <v>1080938</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>qual_MTO_MJ</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>TEI-J</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità qualità piastrella (MTO)</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="8" t="n">
-        <v>864750</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>RI_MJ</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>EFA-J</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Resource Intake (materiali+energia+acqua)</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="8" t="n">
-        <v>148805760</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>IEQ_MJ</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>EFA-J</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Impact Equivalent (impatti in Joule)</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="8" t="n">
-        <v>22982560</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>WEX_MJ</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>EFA-J</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Waste Exergy (rifiuti/sfridi)</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="8" t="n">
-        <v>8283824</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>CIRC_MJ</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>EFA-J</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Circularity Credit (recuperi/circolarità)</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="8" t="n">
-        <v>9622368</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
-        <is>
-          <t>VA_MJ</t>
-        </is>
-      </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA-J</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Valore aggiunto (→MJ)</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="8" t="n">
-        <v>106477441</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
-        <is>
-          <t>econ_in_MJ</t>
-        </is>
-      </c>
-      <c r="B16" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA-J</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Input economici non fisici (→MJ)</t>
-        </is>
-      </c>
-      <c r="D16" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="8" t="n">
-        <v>28728200</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
-        <is>
-          <t>INV_MJ</t>
-        </is>
-      </c>
-      <c r="B17" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA-J</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Immobilizzi (→MJ)</t>
-        </is>
-      </c>
-      <c r="D17" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="8" t="n">
-        <v>13244016</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>SV_MJ</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>SFA-J</t>
-        </is>
-      </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Valore per stakeholder (→MJ)</t>
-        </is>
-      </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="8" t="n">
-        <v>46583880</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>train_MJ</t>
-        </is>
-      </c>
-      <c r="B19" s="5" t="inlineStr">
-        <is>
-          <t>SFA-J</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Credito formazione (→MJ)</t>
-        </is>
-      </c>
-      <c r="D19" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="8" t="n">
-        <v>3071076</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>lost_MJ</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>SFA-J</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Capacità lavorativa persa (→MJ)</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="8" t="n">
-        <v>3106434</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="inlineStr">
-        <is>
-          <t>CO2_MJ</t>
-        </is>
-      </c>
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>SFA-J</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Emissioni CO₂ (→MJ)</t>
-        </is>
-      </c>
-      <c r="D21" s="5" t="inlineStr">
-        <is>
-          <t>MJ</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="8" t="n">
-        <v>16214070</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>Psi</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="inlineStr">
-        <is>
-          <t>exergia</t>
-        </is>
-      </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Ψ = Ex_useful/Ex_ref (efficienza exergetica II principio)</t>
-        </is>
-      </c>
-      <c r="D22" s="5" t="inlineStr">
-        <is>
-          <t>adim.</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="8" t="n">
-        <v>0.164</v>
-      </c>
-      <c r="G22" s="5" t="inlineStr"/>
+          <t>fonte_dati</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Sistema/fonte ed estrazione (ERP/MES/HSE, data)</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr"/>
+      <c r="D9" s="6" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1372,32 +942,33 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:H22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>D020 — periodo omologo 2022 (stesso intervallo, da compilare)</t>
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>D020 — periodo gennaio → cessazione 2025 (DA COMPILARE con dati reali)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="3" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>modulo</t>
         </is>
@@ -1407,24 +978,29 @@
           <t>descrizione</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>unità</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
+          <t>definizione operativa</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>aggancio RP / manuale</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
           <t>VALORE REALE (da compilare)</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>valore provvisorio (in uso, da sostituire)</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>note</t>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>valore provvisorio (in uso)</t>
         </is>
       </c>
     </row>
@@ -1436,10 +1012,10 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>produzione</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
         <is>
           <t>Produzione del periodo</t>
         </is>
@@ -1449,11 +1025,20 @@
           <t>m²</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="8" t="n">
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Quantità di piastrelle prodotte (equivalente) nel periodo di esercizio.</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4; foglio 'Unita'; pesa la media di Gruppo (Tab.10)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="9" t="n">
         <v>2382600</v>
       </c>
-      <c r="G3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -1463,12 +1048,12 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>Gas naturale consumato nel periodo</t>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Gas naturale consumato</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
@@ -1476,11 +1061,20 @@
           <t>Nm³</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="8" t="n">
-        <v>2405291</v>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Volume di metano consumato nel periodo (tutti gli usi di fabbrica).</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4 → Ex_fuel=V·GAS_EX (ADR-012); RP6.2</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="9" t="n">
+        <v>2201068</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -1490,12 +1084,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>energia</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Energia elettrica (inclusa autoproduzione)</t>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Energia elettrica (incl. autoproduzione)</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -1503,11 +1097,20 @@
           <t>kWh</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="8" t="n">
-        <v>7015433</v>
-      </c>
-      <c r="G5" s="5" t="inlineStr"/>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Energia elettrica totale del periodo, inclusa quella autoprodotta dal cogeneratore.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4 → Ex_el=kWh·EL_EX (ADR-012); RP6.1 (cogenerazione)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="9" t="n">
+        <v>6419783</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -1520,9 +1123,9 @@
           <t>TEI-J</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>TEI — perdita exergetica stadio MTS (spray-dryer)</t>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Perdita exergetica stadio MTS (spray-dryer)</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -1530,11 +1133,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="8" t="n">
-        <v>37883340</v>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa nella preparazione impasto/atomizzazione (push).</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J §MTS; RP6.1; RP7.3 Tab.5 (f_tech)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="9" t="n">
+        <v>31064339</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -1547,9 +1159,9 @@
           <t>TEI-J</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>TEI — perdita exergetica stadio MTO (forming/kiln/finishing)</t>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Perdita exergetica stadio MTO (forming/kiln/finishing)</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
@@ -1557,11 +1169,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="8" t="n">
-        <v>32832228</v>
-      </c>
-      <c r="G7" s="5" t="inlineStr"/>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa nelle fasi di formatura, cottura, finitura (pull).</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J §MTO; RP6.1; RP7.3 Tab.5 (f_tech)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="9" t="n">
+        <v>26922427</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -1574,9 +1195,9 @@
           <t>TEI-J</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità exergetica invenduto</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Penalità exergetica invenduto</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
@@ -1584,11 +1205,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="8" t="n">
-        <v>3788334</v>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Exergia immobilizzata nel prodotto non venduto nel periodo.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_inv); RP6.1; RP7.3 Tab.5</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="9" t="n">
+        <v>3174624</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -1601,9 +1231,9 @@
           <t>TEI-J</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità qualità corpo (MTS)</t>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Penalità qualità corpo (MTS)</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1611,11 +1241,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="8" t="n">
-        <v>1262778</v>
-      </c>
-      <c r="G9" s="5" t="inlineStr"/>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Exergia-equivalente delle non conformità sul semilavorato/corpo.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_qual MTS); RP6.1</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="9" t="n">
+        <v>1080938</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -1628,9 +1267,9 @@
           <t>TEI-J</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>TEI — penalità qualità piastrella (MTO)</t>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Penalità qualità piastrella (MTO)</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -1638,11 +1277,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="8" t="n">
-        <v>1010222</v>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Exergia-equivalente delle non conformità sulla piastrella finita.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_qual MTO); RP6.1</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="9" t="n">
+        <v>864750</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -1655,9 +1303,9 @@
           <t>EFA-J</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Resource Intake (materiali+energia+acqua)</t>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Resource Intake (materiali+energia+acqua)</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
@@ -1665,11 +1313,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="8" t="n">
-        <v>151533360</v>
-      </c>
-      <c r="G11" s="5" t="inlineStr"/>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Domanda exergetica delle risorse in ingresso nel periodo.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (RI); RP6.2; RP7.3 Tab.5 (f_env)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="9" t="n">
+        <v>148805760</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -1682,9 +1339,9 @@
           <t>EFA-J</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Impact Equivalent (impatti in Joule)</t>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Impact Equivalent (impatti in Joule)</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -1692,11 +1349,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="8" t="n">
-        <v>25255560</v>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Impatti ambientali (CO₂-eq, ecc.) convertiti in Joule via γ.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (IEQ); RP6.2</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="9" t="n">
+        <v>22982560</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -1709,9 +1375,9 @@
           <t>EFA-J</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Waste Exergy (rifiuti/sfridi)</t>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Waste Exergy (rifiuti/sfridi)</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
@@ -1719,11 +1385,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="8" t="n">
-        <v>10102224</v>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa in rifiuti e sfridi non recuperati.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (WEX); RP6.2</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="9" t="n">
+        <v>8283824</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -1736,9 +1411,9 @@
           <t>EFA-J</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>EFA — Circularity Credit (recuperi/circolarità)</t>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Circularity Credit (recuperi/circolarità)</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -1746,11 +1421,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="8" t="n">
-        <v>7576668</v>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Crediti exergetici da recuperi termici e materia secondaria.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (CIRC); RP6.2; DNSH</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="9" t="n">
+        <v>9622368</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -1763,9 +1447,9 @@
           <t>EcoFA-J</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Valore aggiunto (→MJ)</t>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Valore aggiunto (→MJ)</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
@@ -1773,11 +1457,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="8" t="n">
-        <v>101022240</v>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Valore aggiunto del periodo convertito in equivalente exergetico (€→MJ).</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_VA); RP6.4; RP7.3 Tab.5 (f_econ)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="9" t="n">
+        <v>106477441</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -1790,9 +1483,9 @@
           <t>EcoFA-J</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Input economici non fisici (→MJ)</t>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Input economici non fisici (→MJ)</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
@@ -1800,11 +1493,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="8" t="n">
-        <v>31569450</v>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Servizi terzi/logistica/licenze non già fisici, in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_econ,in); RP6.4</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="9" t="n">
+        <v>28728200</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -1817,9 +1519,9 @@
           <t>EcoFA-J</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>EcoFA — Immobilizzi (→MJ)</t>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Immobilizzi (→MJ)</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
@@ -1827,11 +1529,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="8" t="n">
-        <v>15153336</v>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Scorte/WIP/crediti del periodo in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_INV); RP6.4</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="9" t="n">
+        <v>13244016</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -1844,9 +1555,9 @@
           <t>SFA-J</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Valore per stakeholder (→MJ)</t>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Valore per stakeholder (→MJ)</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -1854,11 +1565,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="8" t="n">
-        <v>44197230</v>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Valore distribuito agli stakeholder nel periodo, in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_SV); RP6.3; RP7.3 Tab.5 (f_soc)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="9" t="n">
+        <v>46583880</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1871,9 +1591,9 @@
           <t>SFA-J</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Credito formazione (→MJ)</t>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Credito formazione (→MJ)</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
@@ -1881,11 +1601,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="8" t="n">
-        <v>2525556</v>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Ore di formazione valorizzate in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_train); RP6.3</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="9" t="n">
+        <v>3071076</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -1898,9 +1627,9 @@
           <t>SFA-J</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Capacità lavorativa persa (→MJ)</t>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Capacità lavorativa persa (→MJ)</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
@@ -1908,11 +1637,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="8" t="n">
-        <v>3788334</v>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Ore perse (infortuni/assenteismo) in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_lost); RP6.3</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="9" t="n">
+        <v>3106434</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1925,9 +1663,9 @@
           <t>SFA-J</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>SFA — Emissioni CO₂ (→MJ)</t>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Emissioni CO₂ sociali (→MJ)</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
@@ -1935,11 +1673,20 @@
           <t>MJ</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="8" t="n">
-        <v>18941670</v>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Emissioni CO₂ del periodo convertite in MJ-eq (carico sociale).</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_CO2); RP6.3</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="9" t="n">
+        <v>16214070</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -1952,9 +1699,9 @@
           <t>exergia</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
-        <is>
-          <t>Ψ = Ex_useful/Ex_ref (efficienza exergetica II principio)</t>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Ψ = Ex_useful/Ex_ref (efficienza II principio)</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1962,16 +1709,1122 @@
           <t>adim.</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="8" t="n">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Efficienza exergetica di secondo principio del periodo (intensiva).</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>RP6.5; ADR-012 (item aperto Ex_useful); RP7.3 Tab.4/7</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="9" t="n">
         <v>0.164</v>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="46" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>D020 — periodo omologo 2022 (stesso intervallo, DA COMPILARE con dati reali)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>modulo</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>descrizione</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>unità</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>definizione operativa</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>aggancio RP / manuale</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>VALORE REALE (da compilare)</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>valore provvisorio (in uso)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>produzione_m2</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>Produzione del periodo</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="inlineStr">
+        <is>
+          <t>Quantità di piastrelle prodotte (equivalente) nel periodo di esercizio.</t>
+        </is>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4; foglio 'Unita'; pesa la media di Gruppo (Tab.10)</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="inlineStr"/>
+      <c r="H3" s="9" t="n">
+        <v>2382600</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>V_gas_Nm3</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Gas naturale consumato</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Nm³</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Volume di metano consumato nel periodo (tutti gli usi di fabbrica).</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4 → Ex_fuel=V·GAS_EX (ADR-012); RP6.2</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="inlineStr"/>
+      <c r="H4" s="9" t="n">
+        <v>2405291</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>E_el_kWh</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Energia</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>Energia elettrica (incl. autoproduzione)</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>kWh</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>Energia elettrica totale del periodo, inclusa quella autoprodotta dal cogeneratore.</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>RP7.3 Tab.4 → Ex_el=kWh·EL_EX (ADR-012); RP6.1 (cogenerazione)</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr"/>
+      <c r="H5" s="9" t="n">
+        <v>7015433</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>loss_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Perdita exergetica stadio MTS (spray-dryer)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa nella preparazione impasto/atomizzazione (push).</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J §MTS; RP6.1; RP7.3 Tab.5 (f_tech)</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr"/>
+      <c r="H6" s="9" t="n">
+        <v>37883340</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>loss_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Perdita exergetica stadio MTO (forming/kiln/finishing)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa nelle fasi di formatura, cottura, finitura (pull).</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J §MTO; RP6.1; RP7.3 Tab.5 (f_tech)</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="9" t="n">
+        <v>32832228</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>inv_MJ</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Penalità exergetica invenduto</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Exergia immobilizzata nel prodotto non venduto nel periodo.</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_inv); RP6.1; RP7.3 Tab.5</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="9" t="n">
+        <v>3788334</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>qual_MTS_MJ</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Penalità qualità corpo (MTS)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>Exergia-equivalente delle non conformità sul semilavorato/corpo.</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_qual MTS); RP6.1</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="inlineStr"/>
+      <c r="H9" s="9" t="n">
+        <v>1262778</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>qual_MTO_MJ</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>TEI-J</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Penalità qualità piastrella (MTO)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Exergia-equivalente delle non conformità sulla piastrella finita.</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Manuale TEI-J (Ex_qual MTO); RP6.1</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="9" t="n">
+        <v>1010222</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>RI_MJ</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>Resource Intake (materiali+energia+acqua)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>Domanda exergetica delle risorse in ingresso nel periodo.</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (RI); RP6.2; RP7.3 Tab.5 (f_env)</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="inlineStr"/>
+      <c r="H11" s="9" t="n">
+        <v>151533360</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>IEQ_MJ</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Impact Equivalent (impatti in Joule)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Impatti ambientali (CO₂-eq, ecc.) convertiti in Joule via γ.</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (IEQ); RP6.2</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="inlineStr"/>
+      <c r="H12" s="9" t="n">
+        <v>25255560</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>WEX_MJ</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>Waste Exergy (rifiuti/sfridi)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>Exergia persa in rifiuti e sfridi non recuperati.</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (WEX); RP6.2</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
+      <c r="H13" s="9" t="n">
+        <v>10102224</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>CIRC_MJ</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>EFA-J</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Circularity Credit (recuperi/circolarità)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Crediti exergetici da recuperi termici e materia secondaria.</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EFA-J (CIRC); RP6.2; DNSH</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="9" t="n">
+        <v>7576668</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>VA_MJ</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>Valore aggiunto (→MJ)</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>Valore aggiunto del periodo convertito in equivalente exergetico (€→MJ).</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_VA); RP6.4; RP7.3 Tab.5 (f_econ)</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="9" t="n">
+        <v>101022240</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>econ_in_MJ</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Input economici non fisici (→MJ)</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Servizi terzi/logistica/licenze non già fisici, in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_econ,in); RP6.4</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="9" t="n">
+        <v>31569450</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>INV_MJ</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>EcoFA-J</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>Immobilizzi (→MJ)</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>Scorte/WIP/crediti del periodo in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>Manuale EcoFA-J (Ex_INV); RP6.4</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="9" t="n">
+        <v>15153336</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>SV_MJ</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>Valore per stakeholder (→MJ)</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>Valore distribuito agli stakeholder nel periodo, in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_SV); RP6.3; RP7.3 Tab.5 (f_soc)</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="9" t="n">
+        <v>44197230</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>train_MJ</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>Credito formazione (→MJ)</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Ore di formazione valorizzate in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_train); RP6.3</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="9" t="n">
+        <v>2525556</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>lost_MJ</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>Capacità lavorativa persa (→MJ)</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>Ore perse (infortuni/assenteismo) in MJ-eq.</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_lost); RP6.3</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr"/>
+      <c r="H20" s="9" t="n">
+        <v>3788334</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>CO2_MJ</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>SFA-J</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>Emissioni CO₂ sociali (→MJ)</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>MJ</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>Emissioni CO₂ del periodo convertite in MJ-eq (carico sociale).</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>Manuale SFA-J (Ex_CO2); RP6.3</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="9" t="n">
+        <v>18941670</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Psi</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>exergia</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>Ψ = Ex_useful/Ex_ref (efficienza II principio)</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>adim.</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>Efficienza exergetica di secondo principio del periodo (intensiva).</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>RP6.5; ADR-012 (item aperto Ex_useful); RP7.3 Tab.4/7</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="9" t="n">
+        <v>0.164</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>dato raccolto</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>dove entra nel modello (start-iids)</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>variabile log beta-1.2</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>tabella/figura RP7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>V_gas_Nm3 / E_el_kWh (2025)</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>foglio 'Energia' (D020,2025) → compute_ex_ref_mj</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>Ex_ref, Psi</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>Tab.4 Bilancio exergetico</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>16 termini moduli (2025)</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>fogli 'Moduli_*' (D020,2025) → compute_f_*</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>f_env,f_econ,f_soc,f_tech,SA_raw,SA_w</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>Tab.5-6 Contributi e SA</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>16 termini moduli (2022 omologo)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>foglio 'Riferimento' (D020,2025) → baseline override</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>(usati come _ref nei f_*)</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Tab.5-6 (nota opzione A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>produzione_m2 (2025)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>foglio 'Unita' (D020,2025) → media di Gruppo pesata</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>(peso di Gruppo)</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>Tab.10 α/β di Gruppo</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>data cessazione / mesi attivi</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>foglio 'Periodo' → guardia TEMPORAL_MISMATCH</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>(months_active)</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Tab.1 Disponibilità; §1.3 Perimetro</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Psi (2025)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>input riportato nel log (ADR-012)</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>Psi → TSI_abs,TSI_rel</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>Tab.7 TSI</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="70" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>controllo</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>regola</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>esito (OK/da sistemare)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Stessa finestra</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>Periodo 2025 e 2022 hanno stesso giorno/mese di inizio e fine</t>
+        </is>
+      </c>
+      <c r="C2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>Durata omologa</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>|giorni_2025 − giorni_2022| ≤ 2 (guardia TEMPORAL_MISMATCH)</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Nessun riproporzionamento</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Valori misurati, non ricavati dall'anno pieno per quota di mesi</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Unità corrette</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>m² / Nm³ / kWh / MJ / adim. come da foglio</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>No doppio conteggio</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Una risorsa in un solo modulo (energia/materiali in EFA/TEI, non in EcoFA)</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Completezza</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Tutti i 20 campi per entrambi i periodi, o annotati se assenti</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Chiusura (ADR-015 §6 / istruzioni §8)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Dati inseriti → run_all beta-1.2 → pytest verde → RP7.3 RV.2 → segnalare RP7.8/RP8.6</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>